--- a/data/trans_dic/P21_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,43; 19,11</t>
+          <t>13,44; 19,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,39; 23,05</t>
+          <t>16,91; 23,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,0; 18,64</t>
+          <t>13,16; 18,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,06; 24,34</t>
+          <t>17,0; 23,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,88; 22,86</t>
+          <t>16,84; 22,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,6; 31,35</t>
+          <t>24,52; 31,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,15; 24,91</t>
+          <t>18,05; 24,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,51; 23,96</t>
+          <t>18,56; 23,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,15; 20,18</t>
+          <t>15,92; 20,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,66; 26,56</t>
+          <t>21,68; 26,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,44; 20,5</t>
+          <t>16,21; 20,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,61; 22,84</t>
+          <t>18,91; 22,95</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,98; 21,94</t>
+          <t>16,77; 21,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,8; 25,32</t>
+          <t>19,95; 25,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,98; 19,96</t>
+          <t>14,94; 20,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,86; 23,55</t>
+          <t>8,57; 23,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,36; 32,32</t>
+          <t>26,11; 32,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,25; 31,86</t>
+          <t>26,24; 32,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,36; 23,6</t>
+          <t>18,53; 23,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,36; 27,46</t>
+          <t>22,17; 27,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,58; 26,43</t>
+          <t>22,35; 26,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,0; 27,75</t>
+          <t>23,71; 27,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,11; 20,81</t>
+          <t>17,42; 21,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,18; 24,28</t>
+          <t>13,32; 24,27</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,25; 21,66</t>
+          <t>15,08; 21,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,89; 27,82</t>
+          <t>21,04; 27,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,38; 19,98</t>
+          <t>14,16; 20,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,55; 23,3</t>
+          <t>16,71; 23,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,45; 29,11</t>
+          <t>22,71; 29,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,84; 36,86</t>
+          <t>29,72; 36,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,98; 22,55</t>
+          <t>17,11; 22,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,49; 72,64</t>
+          <t>24,52; 69,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,79; 24,35</t>
+          <t>19,66; 24,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,15; 31,09</t>
+          <t>26,58; 31,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,23; 20,52</t>
+          <t>16,44; 20,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,94; 54,3</t>
+          <t>21,72; 52,93</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,29; 16,75</t>
+          <t>12,54; 16,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,87; 18,56</t>
+          <t>13,7; 18,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,29; 19,35</t>
+          <t>14,06; 19,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,29; 23,89</t>
+          <t>18,5; 24,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,43; 24,72</t>
+          <t>19,39; 24,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,13; 24,43</t>
+          <t>19,17; 24,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,11; 26,52</t>
+          <t>21,44; 26,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,4; 28,36</t>
+          <t>20,1; 28,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,66; 20,18</t>
+          <t>16,74; 20,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,37; 20,82</t>
+          <t>17,14; 20,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,58; 22,44</t>
+          <t>18,48; 22,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,56; 25,44</t>
+          <t>20,75; 25,51</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,91; 18,54</t>
+          <t>15,73; 18,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,24; 22,17</t>
+          <t>19,3; 22,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,33; 17,98</t>
+          <t>15,4; 17,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,24; 21,67</t>
+          <t>15,17; 21,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,94; 25,86</t>
+          <t>22,94; 25,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,08; 29,2</t>
+          <t>26,13; 29,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,07; 22,89</t>
+          <t>20,19; 23,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,87; 43,22</t>
+          <t>23,92; 42,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,81; 21,78</t>
+          <t>19,83; 21,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,15; 25,26</t>
+          <t>23,13; 25,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,17; 20,13</t>
+          <t>18,16; 20,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,15; 32,19</t>
+          <t>21,47; 32,67</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93187; 132600</t>
+          <t>93263; 133358</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>122231; 161980</t>
+          <t>118855; 165202</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87454; 125434</t>
+          <t>88553; 125839</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>108106; 154268</t>
+          <t>107730; 151388</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>116048; 157168</t>
+          <t>115773; 157462</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>171474; 218544</t>
+          <t>170918; 218628</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>122136; 167583</t>
+          <t>121448; 165182</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>125069; 161896</t>
+          <t>125439; 160903</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>223147; 278710</t>
+          <t>219861; 277765</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>303217; 371805</t>
+          <t>303521; 365540</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>221254; 275881</t>
+          <t>218136; 279036</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>243643; 299053</t>
+          <t>247561; 300492</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>163278; 211035</t>
+          <t>161334; 210904</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>201529; 257712</t>
+          <t>203032; 257180</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>152306; 202907</t>
+          <t>151911; 203897</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>117613; 280962</t>
+          <t>102201; 278550</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>255255; 313033</t>
+          <t>252885; 312661</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>270992; 328888</t>
+          <t>270885; 332494</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>190904; 245316</t>
+          <t>192606; 246972</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>213853; 262607</t>
+          <t>212011; 259144</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>435803; 510203</t>
+          <t>431448; 508260</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>491938; 568994</t>
+          <t>485986; 569452</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>351807; 427814</t>
+          <t>358184; 433193</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>304716; 521869</t>
+          <t>286169; 521654</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>103476; 146966</t>
+          <t>102352; 144290</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>158248; 210807</t>
+          <t>159366; 210659</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109112; 151565</t>
+          <t>107393; 152219</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116629; 164157</t>
+          <t>117730; 166468</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>153553; 199036</t>
+          <t>155300; 200494</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>231596; 286134</t>
+          <t>230720; 284671</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>133088; 176745</t>
+          <t>134136; 179325</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>227640; 675203</t>
+          <t>227968; 643399</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>269544; 331745</t>
+          <t>267878; 330923</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>401115; 476905</t>
+          <t>407739; 481704</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>250359; 316435</t>
+          <t>253605; 316907</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>358489; 887382</t>
+          <t>354914; 865031</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>115681; 157683</t>
+          <t>118074; 158240</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>131188; 175517</t>
+          <t>129571; 176328</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>133704; 181054</t>
+          <t>131535; 178197</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>169494; 221425</t>
+          <t>171429; 222987</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>201841; 256729</t>
+          <t>201335; 254588</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>200803; 256452</t>
+          <t>201197; 254505</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>219932; 276319</t>
+          <t>223413; 279373</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>222815; 309675</t>
+          <t>219548; 308662</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>329909; 399614</t>
+          <t>331529; 399334</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>346579; 415393</t>
+          <t>341940; 416162</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>367511; 443766</t>
+          <t>365484; 439521</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>415137; 513526</t>
+          <t>418863; 514994</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>521268; 607385</t>
+          <t>515224; 602739</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>658662; 759263</t>
+          <t>660984; 758293</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>518647; 608351</t>
+          <t>521233; 605503</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>527034; 749197</t>
+          <t>524524; 755954</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>774989; 873724</t>
+          <t>774864; 872861</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>927222; 1038189</t>
+          <t>928969; 1042891</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>710011; 809947</t>
+          <t>714275; 817333</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>871974; 1578998</t>
+          <t>873901; 1535499</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1317955; 1449133</t>
+          <t>1319432; 1450792</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1615706; 1763105</t>
+          <t>1614116; 1764599</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1257784; 1393367</t>
+          <t>1256781; 1391939</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1504178; 2288957</t>
+          <t>1526592; 2323565</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,44; 19,22</t>
+          <t>13,72; 19,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,91; 23,51</t>
+          <t>17,31; 23,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,16; 18,7</t>
+          <t>12,75; 18,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,0; 23,89</t>
+          <t>16,91; 23,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,84; 22,91</t>
+          <t>16,9; 23,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,52; 31,36</t>
+          <t>24,23; 31,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,05; 24,55</t>
+          <t>17,94; 24,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,56; 23,81</t>
+          <t>18,42; 23,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,92; 20,11</t>
+          <t>16,06; 20,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,68; 26,11</t>
+          <t>21,56; 26,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,21; 20,74</t>
+          <t>16,48; 20,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,91; 22,95</t>
+          <t>18,5; 22,53</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,77; 21,93</t>
+          <t>16,85; 22,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,95; 25,26</t>
+          <t>19,79; 25,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,94; 20,06</t>
+          <t>14,76; 19,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,57; 23,35</t>
+          <t>19,47; 25,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,11; 32,29</t>
+          <t>26,45; 32,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,24; 32,21</t>
+          <t>26,5; 32,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,53; 23,76</t>
+          <t>18,42; 23,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,17; 27,1</t>
+          <t>22,08; 26,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,35; 26,33</t>
+          <t>22,49; 26,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,71; 27,78</t>
+          <t>23,96; 27,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,42; 21,07</t>
+          <t>17,29; 20,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,32; 24,27</t>
+          <t>21,56; 25,54</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,08; 21,27</t>
+          <t>15,4; 21,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,04; 27,81</t>
+          <t>21,22; 27,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,16; 20,07</t>
+          <t>14,16; 19,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,71; 23,62</t>
+          <t>16,01; 22,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,71; 29,32</t>
+          <t>22,9; 29,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,72; 36,67</t>
+          <t>29,87; 36,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,11; 22,88</t>
+          <t>16,72; 22,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,52; 69,22</t>
+          <t>24,15; 29,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,66; 24,29</t>
+          <t>19,68; 24,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,58; 31,41</t>
+          <t>26,46; 31,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,44; 20,55</t>
+          <t>16,48; 20,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,72; 52,93</t>
+          <t>20,9; 25,26</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,54; 16,81</t>
+          <t>12,46; 16,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,7; 18,64</t>
+          <t>13,61; 18,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 19,05</t>
+          <t>14,32; 19,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,5; 24,06</t>
+          <t>18,31; 23,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,39; 24,51</t>
+          <t>19,4; 24,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,17; 24,24</t>
+          <t>19,08; 24,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,44; 26,81</t>
+          <t>21,11; 26,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,1; 28,26</t>
+          <t>24,87; 29,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,74; 20,17</t>
+          <t>16,71; 20,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,14; 20,85</t>
+          <t>17,32; 20,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,48; 22,22</t>
+          <t>18,66; 22,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,75; 25,51</t>
+          <t>22,47; 26,02</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,73; 18,4</t>
+          <t>15,89; 18,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,3; 22,15</t>
+          <t>19,09; 22,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,4; 17,89</t>
+          <t>15,53; 18,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,17; 21,86</t>
+          <t>19,27; 22,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,94; 25,84</t>
+          <t>22,88; 25,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,13; 29,33</t>
+          <t>26,2; 29,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,19; 23,1</t>
+          <t>20,17; 23,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,92; 42,03</t>
+          <t>23,84; 26,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,83; 21,8</t>
+          <t>19,78; 21,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,13; 25,28</t>
+          <t>23,18; 25,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,16; 20,11</t>
+          <t>18,27; 20,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,47; 32,67</t>
+          <t>22,02; 24,01</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128631</t>
+          <t>138529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>143094</t>
+          <t>153684</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>271725</t>
+          <t>292213</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93263; 133358</t>
+          <t>95197; 132150</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>118855; 165202</t>
+          <t>121641; 164167</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88553; 125839</t>
+          <t>85794; 123904</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107730; 151388</t>
+          <t>116461; 162657</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>115773; 157462</t>
+          <t>116159; 158133</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>170918; 218628</t>
+          <t>168911; 218959</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>121448; 165182</t>
+          <t>120721; 162851</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>125439; 160903</t>
+          <t>135010; 172120</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>219861; 277765</t>
+          <t>221902; 278499</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>303521; 365540</t>
+          <t>301841; 363959</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>218136; 279036</t>
+          <t>221807; 277861</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>247561; 300492</t>
+          <t>263030; 320289</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>213681</t>
+          <t>234367</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>236136</t>
+          <t>260706</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>449817</t>
+          <t>495073</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>161334; 210904</t>
+          <t>162016; 214463</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>203032; 257180</t>
+          <t>201486; 256629</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>151911; 203897</t>
+          <t>150083; 199911</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>102201; 278550</t>
+          <t>204203; 265233</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>252885; 312661</t>
+          <t>256145; 313279</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>270885; 332494</t>
+          <t>273520; 331841</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>192606; 246972</t>
+          <t>191441; 245111</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>212011; 259144</t>
+          <t>235967; 288414</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>431448; 508260</t>
+          <t>434109; 509971</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>485986; 569452</t>
+          <t>491273; 573678</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>358184; 433193</t>
+          <t>355409; 429668</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>286169; 521654</t>
+          <t>456678; 540918</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>139569</t>
+          <t>152799</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>389764</t>
+          <t>217971</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>529333</t>
+          <t>370771</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>102352; 144290</t>
+          <t>104457; 148278</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>159366; 210659</t>
+          <t>160762; 208923</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107393; 152219</t>
+          <t>107428; 149420</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117730; 166468</t>
+          <t>128610; 181164</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>155300; 200494</t>
+          <t>156576; 201508</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>230720; 284671</t>
+          <t>231863; 286131</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>134136; 179325</t>
+          <t>131018; 177481</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>227968; 643399</t>
+          <t>195210; 241756</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>267878; 330923</t>
+          <t>268060; 327966</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>407739; 481704</t>
+          <t>405923; 478923</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>253605; 316907</t>
+          <t>254234; 316367</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>354914; 865031</t>
+          <t>336807; 407028</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>195043</t>
+          <t>207487</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>277492</t>
+          <t>302368</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>472536</t>
+          <t>509855</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>118074; 158240</t>
+          <t>117312; 158891</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>129571; 176328</t>
+          <t>128707; 177114</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>131535; 178197</t>
+          <t>134013; 179959</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>171429; 222987</t>
+          <t>181328; 236129</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>201335; 254588</t>
+          <t>201528; 257464</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>201197; 254505</t>
+          <t>200287; 254393</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>223413; 279373</t>
+          <t>219937; 275519</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>219548; 308662</t>
+          <t>277971; 329788</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>331529; 399334</t>
+          <t>330930; 403278</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>341940; 416162</t>
+          <t>345618; 415761</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>365484; 439521</t>
+          <t>369031; 439356</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>418863; 514994</t>
+          <t>473607; 548543</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>676924</t>
+          <t>733182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1046486</t>
+          <t>934729</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1723411</t>
+          <t>1667911</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>515224; 602739</t>
+          <t>520496; 605763</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>660984; 758293</t>
+          <t>653775; 753657</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>521233; 605503</t>
+          <t>525366; 610908</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>524524; 755954</t>
+          <t>680550; 786603</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>774864; 872861</t>
+          <t>772794; 869588</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>928969; 1042891</t>
+          <t>931378; 1040224</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>714275; 817333</t>
+          <t>713789; 813841</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>873901; 1535499</t>
+          <t>888878; 978948</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1319432; 1450792</t>
+          <t>1316431; 1454107</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1614116; 1764599</t>
+          <t>1617893; 1765029</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1256781; 1391939</t>
+          <t>1264567; 1399609</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1526592; 2323565</t>
+          <t>1598604; 1743154</t>
         </is>
       </c>
     </row>
